--- a/artfynd/A 6178-2023 artfynd.xlsx
+++ b/artfynd/A 6178-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 6178-2023 artfynd.xlsx
+++ b/artfynd/A 6178-2023 artfynd.xlsx
@@ -1421,7 +1421,7 @@
         <v>51918453</v>
       </c>
       <c r="B8" t="n">
-        <v>57262</v>
+        <v>57484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 6178-2023 artfynd.xlsx
+++ b/artfynd/A 6178-2023 artfynd.xlsx
@@ -1421,7 +1421,7 @@
         <v>51918453</v>
       </c>
       <c r="B8" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 6178-2023 artfynd.xlsx
+++ b/artfynd/A 6178-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1290,32 +1290,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89840547</v>
+        <v>51918453</v>
       </c>
       <c r="B7" t="n">
-        <v>57992</v>
+        <v>57488</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102126</v>
+        <v>102119</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ortolansparv</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza hortulana</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1325,21 +1325,14 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Frögärde, Björksta sn, Vstm</t>
@@ -1376,22 +1369,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
+          <t>2014-05-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
+          <t>2014-05-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,136 +1399,15 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Örjan Sjögren</t>
+          <t>Västmanlands rapportkommitté</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lina Sjögren</t>
+          <t>Roger Kaufmann, Torbjörn Hegedüs, Thomas Strid, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>51918453</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57487</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>102119</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Göktyta</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Jynx torquilla</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Frögärde, Björksta sn, Vstm</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>600621</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6614800</v>
-      </c>
-      <c r="S8" t="n">
-        <v>47</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Västerås</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Björksta</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2014-05-23</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2014-05-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Västmanlands rapportkommitté</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Roger Kaufmann, Torbjörn Hegedüs, Thomas Strid, Ulf Johansson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 6178-2023 artfynd.xlsx
+++ b/artfynd/A 6178-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1409,6 +1409,127 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123991607</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56541</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Frögärde, Björksta sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>600621</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6614800</v>
+      </c>
+      <c r="S8" t="n">
+        <v>47</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Björksta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Thomas Pettersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Thomas Pettersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
